--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -285,7 +285,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1220,7 +1220,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1407,7 +1407,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1667,7 +1667,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2041,7 +2041,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="66.41015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -3893,7 +3893,7 @@
         <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>83</v>
@@ -5339,7 +5339,7 @@
         <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -1301,7 +1301,10 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -8165,9 +8168,11 @@
       <c r="X51" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="Y51" s="2"/>
+      <c r="Y51" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8203,27 +8208,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8249,16 +8254,16 @@
         <v>192</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8286,10 +8291,10 @@
         <v>376</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8307,7 +8312,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8328,10 +8333,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8342,10 +8347,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8368,16 +8373,16 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8427,7 +8432,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8445,27 +8450,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8488,16 +8493,16 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8547,7 +8552,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8565,27 +8570,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8608,19 +8613,19 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8669,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8681,7 +8686,7 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8690,10 +8695,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8704,10 +8709,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8822,10 +8827,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8942,14 +8947,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8971,10 +8976,10 @@
         <v>140</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>143</v>
@@ -9029,7 +9034,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9064,10 +9069,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9090,13 +9095,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9147,7 +9152,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9156,7 +9161,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9168,10 +9173,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9182,10 +9187,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9208,13 +9213,13 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9265,7 +9270,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9274,7 +9279,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9286,10 +9291,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9300,10 +9305,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9329,16 +9334,16 @@
         <v>192</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9366,10 +9371,10 @@
         <v>118</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9387,7 +9392,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9405,10 +9410,10 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>401</v>
@@ -9422,10 +9427,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9451,16 +9456,16 @@
         <v>192</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9488,10 +9493,10 @@
         <v>376</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9509,7 +9514,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9527,10 +9532,10 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>401</v>
@@ -9544,10 +9549,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9570,17 +9575,17 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9629,7 +9634,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9653,7 +9658,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9664,10 +9669,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9693,10 +9698,10 @@
         <v>211</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9747,7 +9752,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9768,10 +9773,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9782,10 +9787,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9808,16 +9813,16 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9867,7 +9872,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9888,10 +9893,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9902,10 +9907,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9928,16 +9933,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9987,7 +9992,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10008,10 +10013,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10022,10 +10027,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10048,19 +10053,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10109,7 +10114,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10130,10 +10135,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10144,10 +10149,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10262,10 +10267,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10382,14 +10387,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10411,10 +10416,10 @@
         <v>140</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>143</v>
@@ -10469,7 +10474,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10504,10 +10509,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10533,13 +10538,13 @@
         <v>192</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O71" t="s" s="2">
         <v>312</v>
@@ -10570,10 +10575,10 @@
         <v>376</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10591,7 +10596,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>94</v>
@@ -10609,7 +10614,7 @@
         <v>83</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>316</v>
@@ -10626,10 +10631,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10652,16 +10657,16 @@
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O72" t="s" s="2">
         <v>375</v>
@@ -10713,7 +10718,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10731,7 +10736,7 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>380</v>
@@ -10748,10 +10753,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10777,13 +10782,13 @@
         <v>192</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>386</v>
@@ -10835,7 +10840,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10870,10 +10875,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10899,16 +10904,16 @@
         <v>192</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10957,7 +10962,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10992,10 +10997,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11021,16 +11026,16 @@
         <v>84</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11079,7 +11084,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11100,10 +11105,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
